--- a/docs/Mapping_casi_uso/cittadinanza/Citt_018.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_018.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="151">
   <si>
     <t>Sezione</t>
   </si>
@@ -297,6 +297,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>flag dichiarante</t>
@@ -517,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
@@ -1480,7 +1486,7 @@
         <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>41</v>
@@ -1543,53 +1549,53 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="2" t="s">
+      <c r="F46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>108</v>
@@ -1598,7 +1604,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>109</v>
@@ -1607,12 +1613,12 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>110</v>
@@ -1621,7 +1627,7 @@
         <v>40</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>111</v>
@@ -1630,12 +1636,12 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>112</v>
@@ -1644,7 +1650,7 @@
         <v>40</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>113</v>
@@ -1653,12 +1659,12 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>114</v>
@@ -1667,44 +1673,44 @@
         <v>40</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>117</v>
@@ -1713,44 +1719,44 @@
         <v>40</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>22</v>
+        <v>118</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>120</v>
@@ -1759,7 +1765,7 @@
         <v>40</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>121</v>
@@ -1768,12 +1774,12 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>122</v>
@@ -1782,7 +1788,7 @@
         <v>40</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>123</v>
@@ -1791,12 +1797,12 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>124</v>
@@ -1805,7 +1811,7 @@
         <v>40</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>125</v>
@@ -1814,44 +1820,44 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C57" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>131</v>
@@ -1865,7 +1871,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>132</v>
@@ -1874,7 +1880,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>133</v>
@@ -1888,7 +1894,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>134</v>
@@ -1897,7 +1903,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>135</v>
@@ -1911,7 +1917,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>136</v>
@@ -1920,7 +1926,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>137</v>
@@ -1934,16 +1940,16 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>139</v>
@@ -1957,7 +1963,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>140</v>
@@ -1966,7 +1972,7 @@
         <v>40</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>141</v>
@@ -1980,7 +1986,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>142</v>
@@ -1989,7 +1995,7 @@
         <v>40</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>143</v>
@@ -2003,7 +2009,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>144</v>
@@ -2012,7 +2018,7 @@
         <v>40</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>145</v>
@@ -2026,19 +2032,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>40</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2049,19 +2055,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2072,16 +2078,16 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>131</v>
@@ -2095,7 +2101,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>132</v>
@@ -2104,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>133</v>
@@ -2118,19 +2124,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2141,16 +2147,16 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>141</v>
@@ -2164,16 +2170,16 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>143</v>
@@ -2187,16 +2193,16 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>145</v>
@@ -2205,6 +2211,29 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>20</v>
       </c>
     </row>
